--- a/price_simulation_strt.xlsx
+++ b/price_simulation_strt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/158fbdbee6b09c04/ab/Screenshows/price_simulation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="200" documentId="8_{3B525800-95D3-4D59-B803-FFC08F53B71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B25B6660-9D17-45EE-B89F-CCE4A5AB7758}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="8_{3B525800-95D3-4D59-B803-FFC08F53B71E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{89B04240-0326-4633-9D64-D3D54606777C}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{41BDC414-53F4-434F-903D-628AB8BCAEA8}"/>
   </bookViews>
@@ -7983,7 +7983,7 @@
     <v>46133</v>
     <v>0</v>
     <v>1</v>
-    <v>639123264000000000,639124644445960941,0</v>
+    <v>639123264000000000,639124811572666881,0</v>
     <v>0</v>
     <v>a1u3p2</v>
     <v>XNAS:GOOG</v>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="B9" s="12">
         <f ca="1">B7*EXP((B3*0.5*B6^2)*B4/B5+B6*SQRT(B4/B5)*_xlfn.NORM.INV(RAND(),0,1))</f>
-        <v>336.18183819438298</v>
+        <v>333.49231974532432</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.4">
@@ -23392,7 +23392,7 @@
       </c>
       <c r="B9" s="12">
         <f ca="1">B7*EXP((B2-0.5*B6^2)*1/B5+B6*SQRT(B4/B5)*_xlfn.NORM.INV(RAND(),0,1))</f>
-        <v>531.23696219019041</v>
+        <v>243.61173695077494</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.45">
